--- a/jpcore-r4b/feature/merge-v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4b/feature/merge-v1.2.0/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-18T11:30:54+00:00</t>
+    <t>2024-07-18T11:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
